--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4283" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4281" uniqueCount="696">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T12:31:04+00:00</t>
+    <t>2025-03-04T08:19:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -657,10 +657,6 @@
   </si>
   <si>
     <t>Other resources *from the patient record* that may be relevant to the event.  The information from these resources was either used to create the instance or is provided to help with its interpretation.  This extension **should not** be used if more specific  inline elements  or extensions are available.  For example, use `Observation.hasMember`  instead of supportingInformation for  representing the members of an Observation panel.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
   </si>
   <si>
     <t>Observation.extension:MesMomentOfMeasurement</t>
@@ -1804,9 +1800,6 @@
   </si>
   <si>
     <t>Observation.method.coding.code</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Observation.method.coding.display</t>
@@ -4814,7 +4807,7 @@
         <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>122</v>
@@ -4840,13 +4833,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>197</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>82</v>
@@ -4868,13 +4861,13 @@
         <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>210</v>
-      </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4960,10 +4953,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4989,16 +4982,16 @@
         <v>114</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -5047,7 +5040,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -5082,10 +5075,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5108,17 +5101,17 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -5167,7 +5160,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5182,19 +5175,19 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AL22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -5202,14 +5195,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5228,17 +5221,17 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -5287,7 +5280,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5302,16 +5295,16 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5322,14 +5315,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5348,16 +5341,16 @@
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5407,7 +5400,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5422,16 +5415,16 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AL24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5442,10 +5435,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5560,10 +5553,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5680,10 +5673,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5709,13 +5702,13 @@
         <v>107</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5765,16 +5758,16 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI27" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>105</v>
@@ -5800,10 +5793,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5829,13 +5822,13 @@
         <v>135</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5864,28 +5857,28 @@
         <v>155</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="Z28" t="s" s="2">
+      <c r="AA28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5920,10 +5913,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5946,16 +5939,16 @@
         <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6005,7 +5998,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -6029,7 +6022,7 @@
         <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -6040,10 +6033,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6069,13 +6062,13 @@
         <v>107</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -6125,7 +6118,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6160,10 +6153,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6189,16 +6182,16 @@
         <v>173</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -6223,11 +6216,11 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -6245,7 +6238,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>93</v>
@@ -6260,19 +6253,19 @@
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -6280,10 +6273,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6306,19 +6299,19 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -6346,16 +6339,16 @@
         <v>177</v>
       </c>
       <c r="Y32" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="Z32" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="Z32" t="s" s="2">
+      <c r="AA32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB32" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="AC32" s="2"/>
       <c r="AD32" t="s" s="2">
@@ -6365,7 +6358,7 @@
         <v>120</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6389,10 +6382,10 @@
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
@@ -6400,13 +6393,13 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="C33" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>82</v>
@@ -6428,19 +6421,19 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6468,11 +6461,11 @@
         <v>177</v>
       </c>
       <c r="Y33" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="Z33" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="Z33" t="s" s="2">
-        <v>288</v>
-      </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6489,7 +6482,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6513,10 +6506,10 @@
         <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -6524,10 +6517,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6642,10 +6635,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6762,10 +6755,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6791,16 +6784,16 @@
         <v>151</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6849,7 +6842,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6870,10 +6863,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6884,10 +6877,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7002,10 +6995,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="B38" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7122,10 +7115,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="B39" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7151,65 +7144,65 @@
         <v>135</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="S39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7230,10 +7223,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7244,10 +7237,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B40" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7273,13 +7266,13 @@
         <v>107</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7329,7 +7322,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7350,10 +7343,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7364,10 +7357,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="B41" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7393,63 +7386,63 @@
         <v>173</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="S41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7470,10 +7463,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7484,10 +7477,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B42" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7513,14 +7506,14 @@
         <v>107</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7530,7 +7523,7 @@
         <v>82</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>82</v>
@@ -7569,7 +7562,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7590,10 +7583,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7604,10 +7597,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="B43" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7630,19 +7623,19 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7691,7 +7684,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7712,10 +7705,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7726,10 +7719,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7755,16 +7748,16 @@
         <v>107</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7813,7 +7806,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7834,10 +7827,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7848,14 +7841,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7874,19 +7867,19 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7914,11 +7907,11 @@
         <v>155</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="Z45" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="Z45" t="s" s="2">
-        <v>372</v>
-      </c>
       <c r="AA45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7935,7 +7928,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>93</v>
@@ -7950,30 +7943,30 @@
         <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="AL45" t="s" s="2">
+      <c r="AM45" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="AM45" t="s" s="2">
+      <c r="AN45" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="AN45" t="s" s="2">
+      <c r="AO45" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AO45" t="s" s="2">
+      <c r="AP45" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>378</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8088,10 +8081,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8208,10 +8201,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8237,16 +8230,16 @@
         <v>151</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8283,7 +8276,7 @@
         <v>82</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AC48" s="2"/>
       <c r="AD48" t="s" s="2">
@@ -8293,7 +8286,7 @@
         <v>120</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8314,10 +8307,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8328,13 +8321,13 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="C49" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>82</v>
@@ -8359,16 +8352,16 @@
         <v>151</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8417,7 +8410,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8438,10 +8431,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8452,10 +8445,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8570,10 +8563,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8690,10 +8683,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="B52" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8719,23 +8712,23 @@
         <v>135</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>82</v>
@@ -8777,7 +8770,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8798,10 +8791,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8812,10 +8805,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8841,13 +8834,13 @@
         <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8897,7 +8890,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8918,10 +8911,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8932,10 +8925,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8961,21 +8954,21 @@
         <v>173</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>82</v>
@@ -9017,7 +9010,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -9038,10 +9031,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -9052,10 +9045,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="B55" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9081,14 +9074,14 @@
         <v>107</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -9137,7 +9130,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9158,10 +9151,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -9172,10 +9165,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B56" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9198,19 +9191,19 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9259,7 +9252,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9280,10 +9273,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9294,10 +9287,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9323,16 +9316,16 @@
         <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9381,7 +9374,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9402,10 +9395,10 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9416,10 +9409,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9442,19 +9435,19 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9503,7 +9496,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9518,19 +9511,19 @@
         <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AL58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -9538,10 +9531,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9564,16 +9557,16 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9623,7 +9616,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9644,13 +9637,13 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -9658,14 +9651,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9684,19 +9677,19 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9745,7 +9738,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9760,19 +9753,19 @@
         <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AL60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
@@ -9780,14 +9773,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9806,19 +9799,19 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9867,7 +9860,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9876,25 +9869,25 @@
         <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AJ61" t="s" s="2">
+      <c r="AK61" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="AK61" t="s" s="2">
+      <c r="AL61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AL61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AN61" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AN61" t="s" s="2">
+      <c r="AO61" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>82</v>
@@ -9902,10 +9895,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9931,13 +9924,13 @@
         <v>129</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9987,7 +9980,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -10008,13 +10001,13 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AO62" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>82</v>
@@ -10022,10 +10015,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10048,17 +10041,17 @@
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -10107,7 +10100,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10122,19 +10115,19 @@
         <v>105</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AL63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AO63" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>82</v>
@@ -10142,10 +10135,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10168,19 +10161,19 @@
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="M64" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -10217,26 +10210,26 @@
         <v>82</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AC64" s="2"/>
       <c r="AD64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE64" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI64" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>105</v>
@@ -10245,30 +10238,30 @@
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP64" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>469</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="C65" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>82</v>
@@ -10290,19 +10283,19 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="M65" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -10351,7 +10344,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10360,7 +10353,7 @@
         <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>105</v>
@@ -10369,27 +10362,27 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AM65" t="s" s="2">
+      <c r="AN65" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="AN65" t="s" s="2">
+      <c r="AO65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP65" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>469</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10504,10 +10497,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10624,10 +10617,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10650,19 +10643,19 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10711,7 +10704,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10732,10 +10725,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10746,10 +10739,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10775,65 +10768,65 @@
         <v>173</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q69" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="P69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q69" t="s" s="2">
+      <c r="R69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="Y69" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="R69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="Y69" t="s" s="2">
+      <c r="Z69" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="Z69" t="s" s="2">
+      <c r="AA69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10854,10 +10847,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10868,10 +10861,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10897,14 +10890,14 @@
         <v>107</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10953,7 +10946,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10974,10 +10967,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10988,10 +10981,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11017,72 +11010,72 @@
         <v>135</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="S71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF71" t="s" s="2">
+      <c r="AG71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI71" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>105</v>
@@ -11094,10 +11087,10 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11108,10 +11101,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11137,65 +11130,65 @@
         <v>173</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="M72" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11216,10 +11209,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11230,10 +11223,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11256,19 +11249,19 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="N73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11296,37 +11289,37 @@
         <v>155</v>
       </c>
       <c r="Y73" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="Z73" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="Z73" t="s" s="2">
+      <c r="AA73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI73" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>105</v>
@@ -11341,7 +11334,7 @@
         <v>196</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11352,14 +11345,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11378,19 +11371,19 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11418,11 +11411,11 @@
         <v>155</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="Z74" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="Z74" t="s" s="2">
-        <v>538</v>
-      </c>
       <c r="AA74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11439,7 +11432,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11457,27 +11450,27 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="AN74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>542</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11500,19 +11493,19 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11561,7 +11554,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11582,10 +11575,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11596,10 +11589,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11622,16 +11615,16 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11661,7 +11654,7 @@
       </c>
       <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
@@ -11679,7 +11672,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11697,27 +11690,27 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="AM76" t="s" s="2">
+      <c r="AN76" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>559</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11740,19 +11733,19 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="N77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11777,11 +11770,11 @@
         <v>82</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>82</v>
@@ -11799,7 +11792,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11820,10 +11813,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11834,10 +11827,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11952,10 +11945,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12046,7 +12039,7 @@
         <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>122</v>
@@ -12061,7 +12054,7 @@
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -12072,10 +12065,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12101,16 +12094,16 @@
         <v>151</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="N80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12159,7 +12152,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12168,7 +12161,7 @@
         <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>105</v>
@@ -12180,10 +12173,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12194,10 +12187,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12312,10 +12305,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12406,7 +12399,7 @@
         <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>122</v>
@@ -12421,7 +12414,7 @@
         <v>82</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12432,10 +12425,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12461,16 +12454,16 @@
         <v>135</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="N83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12519,7 +12512,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12528,7 +12521,7 @@
         <v>93</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>105</v>
@@ -12540,10 +12533,10 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12554,10 +12547,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12583,13 +12576,13 @@
         <v>107</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12639,7 +12632,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12648,7 +12641,7 @@
         <v>93</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>105</v>
@@ -12660,10 +12653,10 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12674,10 +12667,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12703,16 +12696,14 @@
         <v>173</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" s="2"/>
+      <c r="O85" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12761,7 +12752,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12770,7 +12761,7 @@
         <v>93</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>105</v>
@@ -12782,10 +12773,10 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12796,10 +12787,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12825,16 +12816,14 @@
         <v>107</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" s="2"/>
+      <c r="O86" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12883,7 +12872,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12892,7 +12881,7 @@
         <v>93</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>105</v>
@@ -12904,10 +12893,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12918,10 +12907,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12944,19 +12933,19 @@
         <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="N87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -13005,7 +12994,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13014,7 +13003,7 @@
         <v>93</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>105</v>
@@ -13026,10 +13015,10 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -13040,10 +13029,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13069,16 +13058,16 @@
         <v>107</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -13127,7 +13116,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13136,7 +13125,7 @@
         <v>93</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>105</v>
@@ -13148,10 +13137,10 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13162,10 +13151,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13188,16 +13177,16 @@
         <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13247,7 +13236,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13265,27 +13254,27 @@
         <v>82</v>
       </c>
       <c r="AL89" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="AM89" t="s" s="2">
+      <c r="AO89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP89" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP89" t="s" s="2">
-        <v>588</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13308,16 +13297,16 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="L90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13367,7 +13356,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13385,27 +13374,27 @@
         <v>82</v>
       </c>
       <c r="AL90" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AN90" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="AM90" t="s" s="2">
+      <c r="AO90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP90" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP90" t="s" s="2">
-        <v>597</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13428,19 +13417,19 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="L91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13489,7 +13478,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13501,19 +13490,19 @@
         <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13524,10 +13513,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13642,10 +13631,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13762,14 +13751,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13791,16 +13780,16 @@
         <v>114</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13849,7 +13838,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13884,10 +13873,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13910,13 +13899,13 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="L95" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13967,7 +13956,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13976,7 +13965,7 @@
         <v>93</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>105</v>
@@ -13988,10 +13977,10 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -14002,10 +13991,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14028,13 +14017,13 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14085,7 +14074,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14094,7 +14083,7 @@
         <v>93</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>105</v>
@@ -14106,10 +14095,10 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -14120,10 +14109,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14146,19 +14135,19 @@
         <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -14186,10 +14175,10 @@
         <v>177</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>82</v>
@@ -14207,7 +14196,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14225,13 +14214,13 @@
         <v>82</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14242,10 +14231,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14268,19 +14257,19 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="N98" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="O98" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
@@ -14308,10 +14297,10 @@
         <v>163</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -14329,7 +14318,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14347,13 +14336,13 @@
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14364,10 +14353,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14390,17 +14379,17 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -14449,7 +14438,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14473,7 +14462,7 @@
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14484,10 +14473,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14513,10 +14502,10 @@
         <v>107</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14567,7 +14556,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14588,10 +14577,10 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14602,10 +14591,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14628,16 +14617,16 @@
         <v>94</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>653</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14687,7 +14676,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14708,10 +14697,10 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14722,10 +14711,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14748,16 +14737,16 @@
         <v>94</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>662</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14807,7 +14796,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14828,10 +14817,10 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14842,10 +14831,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14868,19 +14857,19 @@
         <v>94</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="O103" t="s" s="2">
         <v>665</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>667</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14929,7 +14918,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14941,19 +14930,19 @@
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="AN103" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>670</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14964,10 +14953,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15082,10 +15071,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15202,14 +15191,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -15231,16 +15220,16 @@
         <v>114</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15289,7 +15278,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15324,10 +15313,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15350,19 +15339,19 @@
         <v>94</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="N107" t="s" s="2">
         <v>675</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -15390,11 +15379,11 @@
         <v>155</v>
       </c>
       <c r="Y107" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="Z107" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="Z107" t="s" s="2">
-        <v>372</v>
-      </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
       </c>
@@ -15411,7 +15400,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>93</v>
@@ -15429,16 +15418,16 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AM107" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="AN107" t="s" s="2">
+      <c r="AO107" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>82</v>
@@ -15446,10 +15435,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15472,19 +15461,19 @@
         <v>94</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>681</v>
       </c>
-      <c r="L108" t="s" s="2">
+      <c r="N108" t="s" s="2">
         <v>682</v>
       </c>
-      <c r="M108" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>684</v>
-      </c>
       <c r="O108" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15509,40 +15498,40 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>274</v>
+        <v>155</v>
       </c>
       <c r="Y108" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI108" t="s" s="2">
         <v>685</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>105</v>
@@ -15551,27 +15540,27 @@
         <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="AM108" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AN108" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="AN108" t="s" s="2">
+      <c r="AO108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP108" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP108" t="s" s="2">
-        <v>469</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15594,19 +15583,19 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="N109" t="s" s="2">
         <v>690</v>
       </c>
-      <c r="M109" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>692</v>
-      </c>
       <c r="O109" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15634,11 +15623,11 @@
         <v>155</v>
       </c>
       <c r="Y109" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="Z109" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="Z109" t="s" s="2">
-        <v>528</v>
-      </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15655,7 +15644,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15664,7 +15653,7 @@
         <v>93</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>105</v>
@@ -15679,7 +15668,7 @@
         <v>196</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
@@ -15690,14 +15679,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15716,19 +15705,19 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="N110" t="s" s="2">
+      <c r="O110" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15756,11 +15745,11 @@
         <v>155</v>
       </c>
       <c r="Y110" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="Z110" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="Z110" t="s" s="2">
-        <v>538</v>
-      </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
       </c>
@@ -15777,7 +15766,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15795,27 +15784,27 @@
         <v>82</v>
       </c>
       <c r="AL110" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AM110" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="AM110" t="s" s="2">
+      <c r="AN110" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="AN110" t="s" s="2">
+      <c r="AO110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP110" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="AO110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP110" t="s" s="2">
-        <v>542</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15841,16 +15830,16 @@
         <v>83</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15899,7 +15888,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15920,10 +15909,10 @@
         <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T08:19:08+00:00</t>
+    <t>2025-03-27T13:15:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T13:15:18+00:00</t>
+    <t>2025-03-27T14:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T14:27:05+00:00</t>
+    <t>2025-03-27T15:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:41:15+00:00</t>
+    <t>2025-03-27T15:45:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:45:03+00:00</t>
+    <t>2025-03-27T15:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:47:29+00:00</t>
+    <t>2025-03-31T07:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:44:46+00:00</t>
+    <t>2025-03-31T07:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:14+00:00</t>
+    <t>2025-03-31T07:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:39+00:00</t>
+    <t>2025-03-31T11:47:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:47:14+00:00</t>
+    <t>2025-03-31T11:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:46:38+00:00</t>
+    <t>2025-03-31T14:05:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T14:05:37+00:00</t>
+    <t>2025-03-31T15:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:50:51+00:00</t>
+    <t>2025-03-31T15:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:55:12+00:00</t>
+    <t>2025-03-31T16:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:04:27+00:00</t>
+    <t>2025-03-31T16:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:16:40+00:00</t>
+    <t>2025-03-31T16:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:26:20+00:00</t>
+    <t>2025-03-31T16:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:37:23+00:00</t>
+    <t>2025-04-01T07:11:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:11:22+00:00</t>
+    <t>2025-04-01T07:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:12:21+00:00</t>
+    <t>2025-04-01T07:12:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T12:26:08+00:00</t>
+    <t>2025-07-07T09:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T09:50:30+00:00</t>
+    <t>2025-12-23T16:18:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5313,7 +5313,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>233</v>
       </c>
@@ -6151,7 +6151,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>268</v>
       </c>
@@ -6391,7 +6391,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>291</v>
       </c>
@@ -6753,7 +6753,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>297</v>
       </c>
@@ -7113,7 +7113,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>310</v>
       </c>
@@ -7355,7 +7355,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>328</v>
       </c>
@@ -7839,7 +7839,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>364</v>
       </c>
@@ -9407,7 +9407,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>401</v>
       </c>
@@ -9771,7 +9771,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
         <v>428</v>
       </c>
@@ -10253,7 +10253,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>469</v>
       </c>
@@ -10615,7 +10615,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>475</v>
       </c>
@@ -10859,7 +10859,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>496</v>
       </c>
@@ -10979,7 +10979,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
         <v>504</v>
       </c>
@@ -11099,7 +11099,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
         <v>513</v>
       </c>
@@ -11221,7 +11221,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
         <v>521</v>
       </c>
@@ -11705,7 +11705,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
         <v>559</v>
       </c>
@@ -13269,7 +13269,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
         <v>587</v>
       </c>
@@ -14829,7 +14829,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="103" hidden="true">
+    <row r="103">
       <c r="A103" t="s" s="2">
         <v>662</v>
       </c>
@@ -15311,7 +15311,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="107" hidden="true">
+    <row r="107">
       <c r="A107" t="s" s="2">
         <v>672</v>
       </c>
@@ -15433,7 +15433,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="108" hidden="true">
+    <row r="108">
       <c r="A108" t="s" s="2">
         <v>678</v>
       </c>
@@ -15555,7 +15555,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="109" hidden="true">
+    <row r="109">
       <c r="A109" t="s" s="2">
         <v>687</v>
       </c>
@@ -15923,12 +15923,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP111">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T16:18:55+00:00</t>
+    <t>2026-01-06T09:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T09:57:05+00:00</t>
+    <t>2026-01-06T10:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$114</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4281" uniqueCount="696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4395" uniqueCount="709">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T10:01:17+00:00</t>
+    <t>2026-01-19T08:51:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -439,7 +439,7 @@
 </t>
   </si>
   <si>
-    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’un oid : « urn:oid:xx.xx.xx »</t>
+    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
   </si>
   <si>
     <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
@@ -657,6 +657,48 @@
   </si>
   <si>
     <t>Other resources *from the patient record* that may be relevant to the event.  The information from these resources was either used to create the instance or is provided to help with its interpretation.  This extension **should not** be used if more specific  inline elements  or extensions are available.  For example, use `Observation.hasMember`  instead of supportingInformation for  representing the members of an Observation panel.</t>
+  </si>
+  <si>
+    <t>Observation.extension:supportingInfo</t>
+  </si>
+  <si>
+    <t>supportingInfo</t>
+  </si>
+  <si>
+    <t>Autres ressources pertinentes *du dossier patient*</t>
+  </si>
+  <si>
+    <t>Observation.extension:MesReasonForMeasurement</t>
+  </si>
+  <si>
+    <t>MesReasonForMeasurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-reason-for-measurement}
+</t>
+  </si>
+  <si>
+    <t>Motif de la mesure</t>
+  </si>
+  <si>
+    <t>Motif de la mesure
+Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
+  </si>
+  <si>
+    <t>Observation.extension:MesOriginOfData</t>
+  </si>
+  <si>
+    <t>MesOriginOfData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
+</t>
+  </si>
+  <si>
+    <t>Origine de la donnée</t>
+  </si>
+  <si>
+    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
   </si>
   <si>
     <t>Observation.extension:MesMomentOfMeasurement</t>
@@ -1264,7 +1306,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
 </t>
   </si>
   <si>
@@ -1318,7 +1360,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter)
 </t>
   </si>
   <si>
@@ -1413,7 +1455,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -2503,7 +2545,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP111"/>
+  <dimension ref="A1:AP114"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.2109375" customWidth="true" bestFit="true"/>
@@ -2516,7 +2558,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="191.30859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="232.12890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -4861,13 +4903,13 @@
         <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4953,46 +4995,44 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="C21" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="B21" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>114</v>
+        <v>211</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O21" t="s" s="2">
         <v>213</v>
       </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>82</v>
       </c>
@@ -5040,7 +5080,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -5064,7 +5104,7 @@
         <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -5075,12 +5115,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="C22" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="B22" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>82</v>
       </c>
@@ -5089,7 +5131,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
@@ -5098,7 +5140,7 @@
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
         <v>216</v>
@@ -5110,9 +5152,7 @@
         <v>218</v>
       </c>
       <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>219</v>
-      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
       </c>
@@ -5160,7 +5200,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5172,22 +5212,22 @@
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>220</v>
+        <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>222</v>
+        <v>82</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>223</v>
+        <v>82</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -5195,21 +5235,23 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="D23" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
@@ -5218,21 +5260,19 @@
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>229</v>
-      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
@@ -5280,7 +5320,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5292,19 +5332,19 @@
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>230</v>
+        <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>231</v>
+        <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5313,46 +5353,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>234</v>
+        <v>113</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I24" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I24" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="J24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>235</v>
+        <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -5400,7 +5442,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5412,19 +5454,19 @@
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>240</v>
+        <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>241</v>
+        <v>196</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5435,10 +5477,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5449,7 +5491,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -5458,19 +5500,21 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>107</v>
+        <v>229</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>108</v>
+        <v>230</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>109</v>
+        <v>231</v>
       </c>
       <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+      <c r="O25" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5518,34 +5562,34 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>110</v>
+        <v>228</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>82</v>
+        <v>233</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>82</v>
+        <v>234</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>111</v>
+        <v>235</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>82</v>
+        <v>236</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -5553,14 +5597,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>113</v>
+        <v>238</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5576,21 +5620,21 @@
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>114</v>
+        <v>239</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>115</v>
+        <v>240</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5626,19 +5670,19 @@
         <v>82</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>121</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5650,19 +5694,19 @@
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>82</v>
+        <v>243</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>82</v>
+        <v>244</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>111</v>
+        <v>245</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -5671,16 +5715,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>82</v>
+        <v>247</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5690,7 +5734,7 @@
         <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>82</v>
@@ -5699,16 +5743,16 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>107</v>
+        <v>248</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5758,31 +5802,31 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>249</v>
+        <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>196</v>
+        <v>254</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5793,10 +5837,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5816,20 +5860,18 @@
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>251</v>
+        <v>108</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5854,13 +5896,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>255</v>
+        <v>82</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5878,7 +5920,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>256</v>
+        <v>110</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5890,7 +5932,7 @@
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5902,7 +5944,7 @@
         <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5913,21 +5955,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5936,19 +5978,19 @@
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>216</v>
+        <v>114</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>258</v>
+        <v>115</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>259</v>
+        <v>116</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>260</v>
+        <v>117</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5986,31 +6028,31 @@
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>261</v>
+        <v>121</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -6022,7 +6064,7 @@
         <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>262</v>
+        <v>111</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -6033,10 +6075,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6062,13 +6104,13 @@
         <v>107</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -6118,7 +6160,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6127,7 +6169,7 @@
         <v>93</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>105</v>
@@ -6151,12 +6193,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6164,35 +6206,33 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -6216,11 +6256,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="Y31" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="Z31" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -6238,10 +6280,10 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>93</v>
@@ -6253,19 +6295,19 @@
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>275</v>
+        <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>277</v>
+        <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>278</v>
+        <v>196</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>279</v>
+        <v>82</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -6273,10 +6315,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6284,35 +6326,33 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J32" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K32" t="s" s="2">
-        <v>281</v>
+        <v>229</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -6336,35 +6376,37 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AC32" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
@@ -6382,59 +6424,55 @@
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J33" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K33" t="s" s="2">
-        <v>281</v>
+        <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6458,13 +6496,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -6488,7 +6526,7 @@
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
@@ -6506,21 +6544,21 @@
         <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>289</v>
+        <v>196</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6528,31 +6566,35 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>108</v>
+        <v>282</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6576,13 +6618,11 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>82</v>
+        <v>287</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6600,10 +6640,10 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>110</v>
+        <v>281</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>93</v>
@@ -6612,22 +6652,22 @@
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>82</v>
+        <v>288</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>111</v>
+        <v>291</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -6635,24 +6675,24 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
@@ -6661,18 +6701,20 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>114</v>
+        <v>294</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>115</v>
+        <v>295</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>116</v>
+        <v>296</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6696,23 +6738,21 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="AC35" s="2"/>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6720,7 +6760,7 @@
         <v>120</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>121</v>
+        <v>293</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6732,7 +6772,7 @@
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -6744,10 +6784,10 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>111</v>
+        <v>302</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>82</v>
+        <v>303</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
@@ -6755,12 +6795,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="D36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6769,7 +6811,7 @@
         <v>93</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>94</v>
@@ -6778,22 +6820,22 @@
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>151</v>
+        <v>294</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6818,13 +6860,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6842,7 +6884,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6863,13 +6905,13 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>304</v>
+        <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>82</v>
+        <v>303</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -7129,7 +7171,7 @@
         <v>93</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>94</v>
@@ -7141,7 +7183,7 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>312</v>
@@ -7160,55 +7202,55 @@
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="S39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>317</v>
-      </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
@@ -7223,10 +7265,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7237,10 +7279,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B40" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7260,20 +7302,18 @@
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>322</v>
+        <v>108</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -7322,7 +7362,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>325</v>
+        <v>110</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7334,7 +7374,7 @@
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -7343,10 +7383,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>327</v>
+        <v>111</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7355,52 +7395,52 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>173</v>
+        <v>114</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>330</v>
+        <v>115</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>333</v>
+        <v>82</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>82</v>
@@ -7430,31 +7470,31 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>334</v>
+        <v>121</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -7463,10 +7503,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>335</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>336</v>
+        <v>111</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7475,12 +7515,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7488,13 +7528,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>82</v>
@@ -7503,27 +7543,29 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="O42" t="s" s="2">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>333</v>
+        <v>82</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>82</v>
@@ -7562,7 +7604,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7583,10 +7625,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7597,10 +7639,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7623,20 +7665,18 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>347</v>
+        <v>107</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>351</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7684,7 +7724,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7705,10 +7745,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7717,12 +7757,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7730,13 +7770,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>82</v>
@@ -7745,26 +7785,24 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>82</v>
@@ -7806,7 +7844,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7827,10 +7865,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7839,26 +7877,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>365</v>
+        <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>82</v>
@@ -7867,19 +7905,17 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>281</v>
+        <v>107</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7889,7 +7925,7 @@
         <v>82</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>82</v>
@@ -7904,13 +7940,13 @@
         <v>82</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>82</v>
@@ -7928,10 +7964,10 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>93</v>
@@ -7943,30 +7979,30 @@
         <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>372</v>
+        <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>376</v>
+        <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>377</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>378</v>
+        <v>359</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7986,19 +8022,23 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>107</v>
+        <v>360</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>108</v>
+        <v>361</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -8046,7 +8086,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>110</v>
+        <v>365</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8058,7 +8098,7 @@
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -8067,10 +8107,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>111</v>
+        <v>367</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -8081,21 +8121,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -8104,21 +8144,23 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>115</v>
+        <v>370</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>116</v>
+        <v>371</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -8154,31 +8196,31 @@
         <v>82</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>121</v>
+        <v>374</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -8187,10 +8229,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>82</v>
+        <v>375</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>111</v>
+        <v>376</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8199,26 +8241,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>93</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>82</v>
@@ -8227,19 +8269,19 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>151</v>
+        <v>294</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>299</v>
+        <v>379</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>300</v>
+        <v>380</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>301</v>
+        <v>381</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>302</v>
+        <v>382</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8264,35 +8306,37 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>82</v>
+        <v>384</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AC48" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>303</v>
+        <v>377</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
@@ -8301,40 +8345,38 @@
         <v>105</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>82</v>
+        <v>386</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>304</v>
+        <v>387</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>305</v>
+        <v>388</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>82</v>
+        <v>390</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>93</v>
@@ -8346,23 +8388,19 @@
         <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>299</v>
+        <v>108</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -8410,19 +8448,19 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>303</v>
+        <v>110</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -8431,10 +8469,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>304</v>
+        <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>305</v>
+        <v>111</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8445,21 +8483,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -8471,15 +8509,17 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8516,31 +8556,31 @@
         <v>82</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -8563,18 +8603,18 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>81</v>
@@ -8586,21 +8626,23 @@
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>115</v>
+        <v>312</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>116</v>
+        <v>313</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8636,11 +8678,9 @@
         <v>82</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8648,7 +8688,7 @@
         <v>120</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>121</v>
+        <v>316</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8660,7 +8700,7 @@
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8669,10 +8709,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>82</v>
+        <v>317</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>111</v>
+        <v>318</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8683,12 +8723,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="D52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8709,7 +8751,7 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>312</v>
@@ -8728,7 +8770,7 @@
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>390</v>
+        <v>82</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>82</v>
@@ -8770,13 +8812,13 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
@@ -8791,10 +8833,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8805,10 +8847,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8828,20 +8870,18 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>322</v>
+        <v>108</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8890,7 +8930,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>325</v>
+        <v>110</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8902,7 +8942,7 @@
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
@@ -8911,10 +8951,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>327</v>
+        <v>111</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8925,21 +8965,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8948,27 +8988,27 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>173</v>
+        <v>114</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>330</v>
+        <v>115</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>82</v>
@@ -8998,31 +9038,31 @@
         <v>82</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>334</v>
+        <v>121</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -9031,10 +9071,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>335</v>
+        <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>336</v>
+        <v>111</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -9045,10 +9085,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9056,7 +9096,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>93</v>
@@ -9071,24 +9111,26 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="O55" t="s" s="2">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>82</v>
@@ -9130,7 +9172,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9151,10 +9193,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -9165,10 +9207,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9191,20 +9233,18 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>347</v>
+        <v>107</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>351</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -9252,7 +9292,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9273,10 +9313,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9287,10 +9327,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9298,7 +9338,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>93</v>
@@ -9313,26 +9353,24 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
-        <v>82</v>
+        <v>408</v>
       </c>
       <c r="S57" t="s" s="2">
         <v>82</v>
@@ -9374,7 +9412,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9395,10 +9433,10 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9407,12 +9445,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9420,13 +9458,13 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>82</v>
@@ -9435,19 +9473,17 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>402</v>
+        <v>107</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>403</v>
+        <v>352</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>406</v>
+        <v>354</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9496,7 +9532,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>401</v>
+        <v>355</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9511,19 +9547,19 @@
         <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>408</v>
+        <v>356</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>409</v>
+        <v>357</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -9534,7 +9570,7 @@
         <v>411</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9545,7 +9581,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9557,18 +9593,20 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>412</v>
+        <v>360</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>413</v>
+        <v>361</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>414</v>
+        <v>362</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9616,13 +9654,13 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
@@ -9637,13 +9675,13 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>416</v>
+        <v>367</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -9651,14 +9689,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9677,19 +9715,19 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>419</v>
+        <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>420</v>
+        <v>370</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>421</v>
+        <v>371</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>422</v>
+        <v>372</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>423</v>
+        <v>373</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9738,7 +9776,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>417</v>
+        <v>374</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9753,19 +9791,19 @@
         <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>425</v>
+        <v>375</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>426</v>
+        <v>376</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>427</v>
+        <v>82</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
@@ -9773,14 +9811,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>429</v>
+        <v>82</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9799,19 +9837,19 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9860,7 +9898,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9869,25 +9907,25 @@
         <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>435</v>
+        <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>436</v>
+        <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>437</v>
+        <v>420</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>439</v>
+        <v>422</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>440</v>
+        <v>423</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>82</v>
@@ -9895,10 +9933,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>441</v>
+        <v>424</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>441</v>
+        <v>424</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9909,7 +9947,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9921,16 +9959,16 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>129</v>
+        <v>425</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9980,13 +10018,13 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>441</v>
+        <v>424</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
@@ -10001,13 +10039,13 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>445</v>
+        <v>387</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>447</v>
+        <v>423</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>82</v>
@@ -10015,21 +10053,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>82</v>
+        <v>431</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -10041,17 +10079,19 @@
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>449</v>
+        <v>432</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>450</v>
+        <v>433</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="O63" t="s" s="2">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -10100,13 +10140,13 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
@@ -10115,38 +10155,38 @@
         <v>105</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>454</v>
+        <v>438</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>455</v>
+        <v>439</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>456</v>
+        <v>440</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>82</v>
+        <v>442</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>93</v>
@@ -10161,19 +10201,19 @@
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -10210,17 +10250,19 @@
         <v>82</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="AC64" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>463</v>
+        <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10229,40 +10271,38 @@
         <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>105</v>
+        <v>449</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>82</v>
+        <v>450</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>465</v>
+        <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>466</v>
+        <v>451</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>468</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10274,7 +10314,7 @@
         <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>82</v>
@@ -10283,20 +10323,18 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>458</v>
+        <v>129</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10344,7 +10382,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10353,7 +10391,7 @@
         <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>464</v>
+        <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>105</v>
@@ -10362,27 +10400,27 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>465</v>
+        <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>82</v>
+        <v>460</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>468</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10393,7 +10431,7 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>82</v>
@@ -10402,19 +10440,21 @@
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>107</v>
+        <v>462</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>108</v>
+        <v>463</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>109</v>
+        <v>464</v>
       </c>
       <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+      <c r="O66" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
@@ -10462,34 +10502,34 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>110</v>
+        <v>461</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>82</v>
+        <v>466</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>111</v>
+        <v>468</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>82</v>
+        <v>469</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>82</v>
@@ -10497,44 +10537,46 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>114</v>
+        <v>471</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>115</v>
+        <v>472</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>116</v>
+        <v>472</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
@@ -10570,65 +10612,65 @@
         <v>82</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>475</v>
+      </c>
+      <c r="AC67" s="2"/>
       <c r="AD67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>120</v>
+        <v>476</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>121</v>
+        <v>470</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>82</v>
+        <v>478</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>82</v>
+        <v>479</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>111</v>
+        <v>480</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>82</v>
+        <v>481</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="C68" s="2"/>
+        <v>470</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="D68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>93</v>
@@ -10643,19 +10685,19 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10704,7 +10746,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10713,7 +10755,7 @@
         <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>105</v>
@@ -10722,27 +10764,27 @@
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>82</v>
+        <v>478</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>82</v>
+        <v>481</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10759,146 +10801,142 @@
         <v>82</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="P69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q69" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="R69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>498</v>
+        <v>115</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" t="s" s="2">
-        <v>500</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10934,31 +10972,31 @@
         <v>82</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>501</v>
+        <v>121</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -10967,10 +11005,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>502</v>
+        <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>503</v>
+        <v>111</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10981,10 +11019,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>505</v>
+        <v>489</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11007,24 +11045,26 @@
         <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>135</v>
+        <v>490</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>506</v>
+        <v>491</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>492</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>493</v>
+      </c>
       <c r="O71" t="s" s="2">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>509</v>
+        <v>82</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>82</v>
@@ -11066,7 +11106,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>510</v>
+        <v>495</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11075,7 +11115,7 @@
         <v>93</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>511</v>
+        <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>105</v>
@@ -11087,10 +11127,10 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>512</v>
+        <v>497</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11099,12 +11139,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>514</v>
+        <v>499</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11112,16 +11152,16 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I72" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J72" t="s" s="2">
         <v>94</v>
@@ -11130,23 +11170,23 @@
         <v>173</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>516</v>
-      </c>
+        <v>501</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>517</v>
+        <v>502</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q72" s="2"/>
+      <c r="Q72" t="s" s="2">
+        <v>503</v>
+      </c>
       <c r="R72" t="s" s="2">
-        <v>518</v>
+        <v>82</v>
       </c>
       <c r="S72" t="s" s="2">
         <v>82</v>
@@ -11164,13 +11204,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>82</v>
+        <v>286</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>82</v>
+        <v>504</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>82</v>
+        <v>505</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -11188,7 +11228,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11209,10 +11249,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11223,10 +11263,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11234,7 +11274,7 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>93</v>
@@ -11246,22 +11286,20 @@
         <v>82</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>281</v>
+        <v>107</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>524</v>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11286,13 +11324,13 @@
         <v>82</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>526</v>
+        <v>82</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>527</v>
+        <v>82</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>82</v>
@@ -11310,7 +11348,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11319,7 +11357,7 @@
         <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>105</v>
@@ -11331,10 +11369,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>196</v>
+        <v>515</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11343,54 +11381,52 @@
         <v>82</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>530</v>
+        <v>517</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>531</v>
+        <v>82</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>281</v>
+        <v>135</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>534</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>535</v>
+        <v>521</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="S74" t="s" s="2">
         <v>82</v>
@@ -11408,13 +11444,13 @@
         <v>82</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>536</v>
+        <v>82</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>537</v>
+        <v>82</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>82</v>
@@ -11432,16 +11468,16 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>82</v>
+        <v>524</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>105</v>
@@ -11450,27 +11486,27 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>538</v>
+        <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>539</v>
+        <v>515</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>540</v>
+        <v>525</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>541</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11478,41 +11514,41 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>543</v>
+        <v>173</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>544</v>
+        <v>528</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>545</v>
+        <v>528</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>546</v>
+        <v>529</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>547</v>
+        <v>530</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>82</v>
+        <v>531</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>82</v>
@@ -11554,13 +11590,13 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>82</v>
@@ -11575,10 +11611,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>548</v>
+        <v>515</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11587,12 +11623,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11606,7 +11642,7 @@
         <v>93</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>82</v>
@@ -11615,18 +11651,20 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>552</v>
+        <v>536</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>537</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>538</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11650,11 +11688,13 @@
         <v>82</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Y76" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>539</v>
+      </c>
       <c r="Z76" t="s" s="2">
-        <v>554</v>
+        <v>540</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
@@ -11672,7 +11712,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11681,7 +11721,7 @@
         <v>93</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>82</v>
+        <v>541</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>105</v>
@@ -11690,41 +11730,41 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>555</v>
+        <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>556</v>
+        <v>196</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>557</v>
+        <v>542</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>558</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>82</v>
+        <v>544</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>82</v>
@@ -11733,19 +11773,19 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>560</v>
+        <v>545</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>561</v>
+        <v>546</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>562</v>
+        <v>547</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>563</v>
+        <v>548</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11770,11 +11810,13 @@
         <v>82</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="Y77" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>549</v>
+      </c>
       <c r="Z77" t="s" s="2">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>82</v>
@@ -11792,13 +11834,13 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>82</v>
@@ -11810,27 +11852,27 @@
         <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>82</v>
+        <v>551</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>82</v>
+        <v>554</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11841,7 +11883,7 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>82</v>
@@ -11853,16 +11895,20 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>107</v>
+        <v>556</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>108</v>
+        <v>557</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+        <v>558</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>560</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11910,19 +11956,19 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>110</v>
+        <v>555</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
@@ -11931,10 +11977,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>82</v>
+        <v>561</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>111</v>
+        <v>562</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11945,21 +11991,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
@@ -11971,16 +12017,16 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>114</v>
+        <v>294</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>115</v>
+        <v>564</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>116</v>
+        <v>565</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>117</v>
+        <v>566</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12006,69 +12052,67 @@
         <v>82</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>82</v>
+        <v>567</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>121</v>
+        <v>563</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>82</v>
+        <v>568</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>82</v>
+        <v>569</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>111</v>
+        <v>570</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>82</v>
+        <v>571</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12079,31 +12123,31 @@
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>151</v>
+        <v>294</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>299</v>
+        <v>573</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>300</v>
+        <v>574</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>301</v>
+        <v>575</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>302</v>
+        <v>576</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12128,13 +12172,11 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>82</v>
+        <v>577</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -12152,13 +12194,13 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>303</v>
+        <v>572</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
@@ -12173,10 +12215,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>304</v>
+        <v>578</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>305</v>
+        <v>579</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12187,10 +12229,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12305,10 +12347,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>571</v>
+        <v>581</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>571</v>
+        <v>581</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12425,10 +12467,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12436,10 +12478,10 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
@@ -12451,7 +12493,7 @@
         <v>94</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="L83" t="s" s="2">
         <v>312</v>
@@ -12512,13 +12554,13 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
@@ -12533,10 +12575,10 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12547,10 +12589,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>573</v>
+        <v>583</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>573</v>
+        <v>583</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12570,20 +12612,18 @@
         <v>82</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>322</v>
+        <v>108</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12632,7 +12672,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>325</v>
+        <v>110</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12644,7 +12684,7 @@
         <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12653,10 +12693,10 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>327</v>
+        <v>111</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12667,21 +12707,21 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>82</v>
@@ -12690,21 +12730,21 @@
         <v>82</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>173</v>
+        <v>114</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>330</v>
+        <v>115</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12740,31 +12780,31 @@
         <v>82</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>334</v>
+        <v>121</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
@@ -12773,10 +12813,10 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>335</v>
+        <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>336</v>
+        <v>111</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12787,10 +12827,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>575</v>
+        <v>585</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>575</v>
+        <v>585</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12798,7 +12838,7 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>93</v>
@@ -12813,17 +12853,19 @@
         <v>94</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="O86" t="s" s="2">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12872,7 +12914,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12893,10 +12935,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12907,10 +12949,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12933,20 +12975,18 @@
         <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>347</v>
+        <v>107</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>351</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12994,7 +13034,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13015,10 +13055,10 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -13029,10 +13069,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13040,7 +13080,7 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>93</v>
@@ -13055,19 +13095,17 @@
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -13116,7 +13154,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13137,10 +13175,10 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13151,10 +13189,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13174,21 +13212,21 @@
         <v>82</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>579</v>
+        <v>107</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>580</v>
+        <v>352</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="O89" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13236,7 +13274,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>578</v>
+        <v>355</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13254,27 +13292,27 @@
         <v>82</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>583</v>
+        <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>584</v>
+        <v>356</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>585</v>
+        <v>357</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>586</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13288,27 +13326,29 @@
         <v>93</v>
       </c>
       <c r="H90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J90" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K90" t="s" s="2">
-        <v>588</v>
+        <v>360</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>589</v>
+        <v>361</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>590</v>
+        <v>362</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
@@ -13356,7 +13396,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>587</v>
+        <v>365</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13374,27 +13414,27 @@
         <v>82</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>592</v>
+        <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>593</v>
+        <v>366</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>594</v>
+        <v>367</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>595</v>
+        <v>82</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13405,7 +13445,7 @@
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>82</v>
@@ -13414,22 +13454,22 @@
         <v>82</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>597</v>
+        <v>107</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>598</v>
+        <v>370</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>599</v>
+        <v>371</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>600</v>
+        <v>372</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>601</v>
+        <v>373</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13478,19 +13518,19 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>596</v>
+        <v>374</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>602</v>
+        <v>105</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>82</v>
@@ -13499,10 +13539,10 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>603</v>
+        <v>375</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>604</v>
+        <v>376</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13513,10 +13553,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>605</v>
+        <v>591</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>605</v>
+        <v>591</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13539,15 +13579,17 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>107</v>
+        <v>592</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>108</v>
+        <v>593</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>594</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>595</v>
+      </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -13596,7 +13638,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>110</v>
+        <v>591</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13608,47 +13650,47 @@
         <v>82</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>82</v>
+        <v>596</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>82</v>
+        <v>597</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>111</v>
+        <v>598</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>82</v>
+        <v>599</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>82</v>
@@ -13657,16 +13699,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>114</v>
+        <v>601</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>115</v>
+        <v>602</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>116</v>
+        <v>603</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>117</v>
+        <v>604</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13716,49 +13758,49 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>121</v>
+        <v>600</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>82</v>
+        <v>605</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>82</v>
+        <v>606</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>111</v>
+        <v>607</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>82</v>
+        <v>608</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>608</v>
+        <v>82</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13771,25 +13813,25 @@
         <v>82</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>114</v>
+        <v>610</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>117</v>
+        <v>613</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>213</v>
+        <v>614</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13838,7 +13880,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13850,7 +13892,7 @@
         <v>82</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>122</v>
+        <v>615</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>82</v>
@@ -13859,10 +13901,10 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>82</v>
+        <v>616</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>196</v>
+        <v>617</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13873,10 +13915,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13899,13 +13941,13 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>613</v>
+        <v>107</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>614</v>
+        <v>108</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>615</v>
+        <v>109</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13956,7 +13998,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>612</v>
+        <v>110</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13965,10 +14007,10 @@
         <v>93</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>616</v>
+        <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>82</v>
@@ -13977,10 +14019,10 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>617</v>
+        <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>618</v>
+        <v>111</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13998,14 +14040,14 @@
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>82</v>
@@ -14017,15 +14059,17 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>613</v>
+        <v>114</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>620</v>
+        <v>115</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="N96" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -14074,19 +14118,19 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>619</v>
+        <v>121</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>616</v>
+        <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
@@ -14095,10 +14139,10 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>617</v>
+        <v>82</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>622</v>
+        <v>111</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -14109,45 +14153,45 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>82</v>
+        <v>621</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>281</v>
+        <v>114</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>626</v>
+        <v>117</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>627</v>
+        <v>226</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -14172,13 +14216,13 @@
         <v>82</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>628</v>
+        <v>82</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>629</v>
+        <v>82</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>82</v>
@@ -14196,31 +14240,31 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>630</v>
+        <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>631</v>
+        <v>82</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>540</v>
+        <v>196</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14231,10 +14275,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14245,7 +14289,7 @@
         <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>82</v>
@@ -14257,20 +14301,16 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>281</v>
+        <v>626</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>636</v>
-      </c>
+        <v>628</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
@@ -14294,13 +14334,13 @@
         <v>82</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>637</v>
+        <v>82</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>638</v>
+        <v>82</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -14318,16 +14358,16 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>82</v>
+        <v>629</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>105</v>
@@ -14336,13 +14376,13 @@
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM98" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="AM98" t="s" s="2">
+      <c r="AN98" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14353,10 +14393,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14379,18 +14419,16 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>640</v>
+        <v>626</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="N99" s="2"/>
-      <c r="O99" t="s" s="2">
-        <v>643</v>
-      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
@@ -14438,7 +14476,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14447,7 +14485,7 @@
         <v>93</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>82</v>
+        <v>629</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>105</v>
@@ -14459,10 +14497,10 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>82</v>
+        <v>630</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14473,10 +14511,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14499,16 +14537,20 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>107</v>
+        <v>294</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+        <v>638</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>640</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
@@ -14532,13 +14574,13 @@
         <v>82</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>82</v>
+        <v>641</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>82</v>
+        <v>642</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>82</v>
@@ -14556,7 +14598,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14574,13 +14616,13 @@
         <v>82</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>82</v>
+        <v>643</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>617</v>
+        <v>644</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>648</v>
+        <v>553</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14591,10 +14633,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14614,21 +14656,23 @@
         <v>82</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>650</v>
+        <v>294</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="O101" s="2"/>
+        <v>648</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>649</v>
+      </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
@@ -14652,13 +14696,13 @@
         <v>82</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>82</v>
+        <v>650</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>82</v>
+        <v>651</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>82</v>
@@ -14676,7 +14720,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14694,13 +14738,13 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>82</v>
+        <v>643</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>655</v>
+        <v>553</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14711,10 +14755,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14725,7 +14769,7 @@
         <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>82</v>
@@ -14734,21 +14778,21 @@
         <v>82</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="O102" s="2"/>
+        <v>655</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" t="s" s="2">
+        <v>656</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
       </c>
@@ -14796,13 +14840,13 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>82</v>
@@ -14817,10 +14861,10 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>654</v>
+        <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14829,12 +14873,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14845,32 +14889,28 @@
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>597</v>
+        <v>107</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>665</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>82</v>
       </c>
@@ -14918,19 +14958,19 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>666</v>
+        <v>105</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>82</v>
@@ -14939,10 +14979,10 @@
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>667</v>
+        <v>630</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14953,10 +14993,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14967,7 +15007,7 @@
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>82</v>
@@ -14976,18 +15016,20 @@
         <v>82</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>107</v>
+        <v>663</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>108</v>
+        <v>664</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N104" s="2"/>
+        <v>665</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>666</v>
+      </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -15036,19 +15078,19 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>110</v>
+        <v>662</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>82</v>
@@ -15057,10 +15099,10 @@
         <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>82</v>
+        <v>667</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>111</v>
+        <v>668</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -15071,14 +15113,14 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -15094,19 +15136,19 @@
         <v>82</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>114</v>
+        <v>670</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>115</v>
+        <v>671</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>116</v>
+        <v>672</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>117</v>
+        <v>673</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15156,7 +15198,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>121</v>
+        <v>669</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15168,7 +15210,7 @@
         <v>82</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>82</v>
@@ -15177,10 +15219,10 @@
         <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>82</v>
+        <v>667</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>111</v>
+        <v>674</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -15189,16 +15231,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="106" hidden="true">
+    <row r="106">
       <c r="A106" t="s" s="2">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>608</v>
+        <v>82</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -15208,28 +15250,28 @@
         <v>81</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J106" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>114</v>
+        <v>610</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>609</v>
+        <v>676</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>610</v>
+        <v>676</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>117</v>
+        <v>677</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>213</v>
+        <v>678</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15278,7 +15320,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>611</v>
+        <v>675</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15290,7 +15332,7 @@
         <v>82</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>122</v>
+        <v>679</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>82</v>
@@ -15299,10 +15341,10 @@
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>82</v>
+        <v>680</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>196</v>
+        <v>681</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15311,12 +15353,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15324,35 +15366,31 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>281</v>
+        <v>107</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>673</v>
+        <v>108</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>676</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>82</v>
       </c>
@@ -15376,13 +15414,13 @@
         <v>82</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -15400,10 +15438,10 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>672</v>
+        <v>110</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>93</v>
@@ -15412,69 +15450,67 @@
         <v>82</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>677</v>
+        <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>374</v>
+        <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>375</v>
+        <v>111</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>376</v>
+        <v>82</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>679</v>
+        <v>114</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>680</v>
+        <v>115</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>681</v>
+        <v>116</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>82</v>
       </c>
@@ -15498,104 +15534,104 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>683</v>
+        <v>82</v>
       </c>
       <c r="Z108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP108" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
         <v>684</v>
       </c>
-      <c r="AA108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP108" t="s" s="2">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s" s="2">
-        <v>687</v>
-      </c>
       <c r="B109" t="s" s="2">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>82</v>
+        <v>621</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I109" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I109" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="J109" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>281</v>
+        <v>114</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>688</v>
+        <v>622</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>689</v>
+        <v>623</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>690</v>
+        <v>117</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>525</v>
+        <v>226</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15620,13 +15656,13 @@
         <v>82</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>526</v>
+        <v>82</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>527</v>
+        <v>82</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
@@ -15644,19 +15680,19 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>687</v>
+        <v>624</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>691</v>
+        <v>82</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>82</v>
@@ -15665,11 +15701,11 @@
         <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN109" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AN109" t="s" s="2">
-        <v>529</v>
-      </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15677,47 +15713,47 @@
         <v>82</v>
       </c>
     </row>
-    <row r="110" hidden="true">
+    <row r="110">
       <c r="A110" t="s" s="2">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>531</v>
+        <v>82</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>532</v>
+        <v>686</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>533</v>
+        <v>687</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>534</v>
+        <v>688</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>535</v>
+        <v>689</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15745,10 +15781,10 @@
         <v>155</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>536</v>
+        <v>383</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>537</v>
+        <v>384</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
@@ -15766,13 +15802,13 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>82</v>
@@ -15784,27 +15820,27 @@
         <v>82</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>538</v>
+        <v>690</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>539</v>
+        <v>387</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>540</v>
+        <v>388</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>541</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="111" hidden="true">
+    <row r="111">
       <c r="A111" t="s" s="2">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15815,31 +15851,31 @@
         <v>80</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>83</v>
+        <v>692</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>694</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>695</v>
       </c>
-      <c r="N111" t="s" s="2">
-        <v>600</v>
-      </c>
       <c r="O111" t="s" s="2">
-        <v>601</v>
+        <v>474</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15864,13 +15900,13 @@
         <v>82</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>82</v>
+        <v>696</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>82</v>
+        <v>697</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>82</v>
@@ -15888,16 +15924,16 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>82</v>
+        <v>698</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>105</v>
@@ -15906,23 +15942,389 @@
         <v>82</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>82</v>
+        <v>699</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>603</v>
+        <v>479</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>604</v>
+        <v>480</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP111" t="s" s="2">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="P112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP112" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="P113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP113" t="s" s="2">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="P114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP114" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP111">
+  <autoFilter ref="A1:AP114">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15932,7 +16334,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI110">
+  <conditionalFormatting sqref="A2:AI113">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T08:51:58+00:00</t>
+    <t>2026-01-19T09:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:23:14+00:00</t>
+    <t>2026-01-19T09:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:39:10+00:00</t>
+    <t>2026-01-19T09:47:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:47:31+00:00</t>
+    <t>2026-01-19T09:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:54:18+00:00</t>
+    <t>2026-01-19T09:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:56:13+00:00</t>
+    <t>2026-01-19T10:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T10:07:50+00:00</t>
+    <t>2026-01-20T07:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T07:44:39+00:00</t>
+    <t>2026-01-20T09:11:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:11:57+00:00</t>
+    <t>2026-01-20T09:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:43:53+00:00</t>
+    <t>2026-01-20T09:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:47:48+00:00</t>
+    <t>2026-01-20T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T10:06:11+00:00</t>
+    <t>2026-01-20T11:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$113</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4395" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4357" uniqueCount="704">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T11:11:06+00:00</t>
+    <t>2026-01-20T12:50:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -683,22 +683,6 @@
   <si>
     <t>Motif de la mesure
 Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
-  </si>
-  <si>
-    <t>Observation.extension:MesOriginOfData</t>
-  </si>
-  <si>
-    <t>MesOriginOfData</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
-</t>
-  </si>
-  <si>
-    <t>Origine de la donnée</t>
-  </si>
-  <si>
-    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
   </si>
   <si>
     <t>Observation.extension:MesMomentOfMeasurement</t>
@@ -2545,7 +2529,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP114"/>
+  <dimension ref="A1:AP113"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.2109375" customWidth="true" bestFit="true"/>
@@ -5149,7 +5133,7 @@
         <v>217</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5235,44 +5219,46 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O23" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="L23" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
@@ -5320,7 +5306,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5344,7 +5330,7 @@
         <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5362,7 +5348,7 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5375,25 +5361,23 @@
         <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="J24" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K24" t="s" s="2">
-        <v>114</v>
+        <v>224</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5442,7 +5426,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5454,22 +5438,22 @@
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>82</v>
+        <v>228</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>82</v>
+        <v>229</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>196</v>
+        <v>230</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>82</v>
+        <v>231</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -5477,14 +5461,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>82</v>
+        <v>233</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5503,17 +5487,17 @@
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5562,7 +5546,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5577,44 +5561,44 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>236</v>
+        <v>82</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>82</v>
@@ -5623,18 +5607,18 @@
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5682,7 +5666,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5697,16 +5681,16 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -5715,16 +5699,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>247</v>
+        <v>82</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5734,26 +5718,24 @@
         <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>248</v>
+        <v>107</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>249</v>
+        <v>108</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5802,31 +5784,31 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>246</v>
+        <v>110</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>254</v>
+        <v>111</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5837,21 +5819,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>82</v>
@@ -5863,15 +5845,17 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5908,31 +5892,31 @@
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5955,21 +5939,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5978,19 +5962,19 @@
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>115</v>
+        <v>253</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>116</v>
+        <v>254</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>117</v>
+        <v>255</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6028,31 +6012,31 @@
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>121</v>
+        <v>256</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -6064,7 +6048,7 @@
         <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>111</v>
+        <v>196</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -6075,10 +6059,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6101,16 +6085,16 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -6136,13 +6120,13 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>82</v>
+        <v>263</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -6160,7 +6144,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6169,7 +6153,7 @@
         <v>93</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>262</v>
+        <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>105</v>
@@ -6195,10 +6179,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6221,16 +6205,16 @@
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>135</v>
+        <v>224</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6256,13 +6240,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>267</v>
+        <v>82</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>268</v>
+        <v>82</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -6304,7 +6288,7 @@
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>196</v>
+        <v>270</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -6315,10 +6299,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6341,16 +6325,16 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>229</v>
+        <v>107</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6400,7 +6384,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6424,7 +6408,7 @@
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>275</v>
+        <v>196</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6433,7 +6417,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>276</v>
       </c>
@@ -6446,22 +6430,22 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>277</v>
@@ -6472,7 +6456,9 @@
       <c r="N33" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="O33" s="2"/>
+      <c r="O33" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6496,13 +6482,11 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -6520,10 +6504,10 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>93</v>
@@ -6535,30 +6519,30 @@
         <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>196</v>
+        <v>286</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>82</v>
+        <v>287</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6569,31 +6553,31 @@
         <v>93</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>94</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>173</v>
+        <v>289</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6618,35 +6602,35 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="Y34" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="Z34" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="AC34" s="2"/>
       <c r="AD34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
@@ -6655,32 +6639,34 @@
         <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AP34" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="35" hidden="true">
-      <c r="A35" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="C35" s="2"/>
+      <c r="C35" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="D35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6689,7 +6675,7 @@
         <v>93</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>94</v>
@@ -6701,19 +6687,19 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6741,26 +6727,28 @@
         <v>177</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="AC35" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6784,37 +6772,35 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AO35" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AP35" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="36" hidden="true">
+      <c r="A36" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AO35" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>305</v>
-      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
@@ -6823,20 +6809,16 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>294</v>
+        <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>295</v>
+        <v>108</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6860,13 +6842,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6884,19 +6866,19 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>293</v>
+        <v>110</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6908,10 +6890,10 @@
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>302</v>
+        <v>111</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -6919,21 +6901,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
@@ -6945,15 +6927,17 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6990,31 +6974,31 @@
         <v>82</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
@@ -7035,46 +7019,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>115</v>
+        <v>307</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>116</v>
+        <v>308</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -7110,19 +7096,19 @@
         <v>82</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>121</v>
+        <v>311</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7134,7 +7120,7 @@
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -7143,10 +7129,10 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>111</v>
+        <v>313</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -7155,12 +7141,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7168,35 +7154,31 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>312</v>
+        <v>108</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -7244,19 +7226,19 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>316</v>
+        <v>110</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -7265,10 +7247,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>317</v>
+        <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>318</v>
+        <v>111</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7279,21 +7261,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -7305,15 +7287,17 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -7350,31 +7334,31 @@
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -7395,52 +7379,54 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>115</v>
+        <v>320</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>116</v>
+        <v>321</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>82</v>
+        <v>324</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>82</v>
@@ -7470,31 +7456,31 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>121</v>
+        <v>325</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -7503,10 +7489,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>82</v>
+        <v>326</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>111</v>
+        <v>327</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7515,12 +7501,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7528,13 +7514,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>82</v>
@@ -7543,26 +7529,24 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>329</v>
+        <v>82</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>82</v>
@@ -7604,7 +7588,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7625,10 +7609,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7637,12 +7621,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7650,13 +7634,13 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>82</v>
@@ -7665,24 +7649,24 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>82</v>
+        <v>341</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>82</v>
@@ -7724,7 +7708,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7745,10 +7729,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7757,12 +7741,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7770,13 +7754,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>82</v>
@@ -7785,27 +7769,27 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>82</v>
+        <v>341</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>82</v>
@@ -7844,7 +7828,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7865,10 +7849,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7879,10 +7863,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7905,17 +7889,19 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>107</v>
+        <v>355</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>358</v>
+      </c>
       <c r="O45" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7925,7 +7911,7 @@
         <v>82</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>82</v>
@@ -7964,7 +7950,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7985,10 +7971,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7999,10 +7985,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8025,19 +8011,19 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>360</v>
+        <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -8086,7 +8072,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8107,10 +8093,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -8119,26 +8105,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>82</v>
+        <v>373</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>82</v>
@@ -8147,19 +8133,19 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>107</v>
+        <v>289</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -8184,13 +8170,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -8208,10 +8194,10 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>93</v>
@@ -8223,66 +8209,62 @@
         <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>82</v>
+        <v>381</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>82</v>
+        <v>384</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>378</v>
+        <v>82</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>294</v>
+        <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>379</v>
+        <v>108</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -8306,13 +8288,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>384</v>
+        <v>82</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -8330,10 +8312,10 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>377</v>
+        <v>110</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>93</v>
@@ -8342,44 +8324,44 @@
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>386</v>
+        <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>388</v>
+        <v>111</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>389</v>
+        <v>82</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>390</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -8391,15 +8373,17 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8436,31 +8420,31 @@
         <v>82</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -8483,18 +8467,18 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>81</v>
@@ -8506,21 +8490,23 @@
         <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>115</v>
+        <v>307</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>116</v>
+        <v>308</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -8556,11 +8542,9 @@
         <v>82</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
         <v>82</v>
       </c>
@@ -8568,7 +8552,7 @@
         <v>120</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>121</v>
+        <v>311</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8580,7 +8564,7 @@
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -8589,10 +8573,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>111</v>
+        <v>313</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8603,12 +8587,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="D51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8617,7 +8603,7 @@
         <v>93</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -8632,16 +8618,16 @@
         <v>151</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8678,17 +8664,19 @@
         <v>82</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AC51" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8709,10 +8697,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8723,20 +8711,18 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="C52" t="s" s="2">
-        <v>396</v>
-      </c>
+      <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>93</v>
@@ -8748,23 +8734,19 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>312</v>
+        <v>108</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8812,19 +8794,19 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>316</v>
+        <v>110</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8833,10 +8815,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>317</v>
+        <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>318</v>
+        <v>111</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8847,21 +8829,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8873,15 +8855,17 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8918,31 +8902,31 @@
         <v>82</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
@@ -8965,21 +8949,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8988,27 +8972,29 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>115</v>
+        <v>320</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>116</v>
+        <v>321</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>82</v>
@@ -9038,31 +9024,31 @@
         <v>82</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>121</v>
+        <v>325</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -9071,10 +9057,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>82</v>
+        <v>326</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>111</v>
+        <v>327</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -9085,10 +9071,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9096,7 +9082,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>93</v>
@@ -9111,26 +9097,24 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>403</v>
+        <v>82</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>82</v>
@@ -9172,7 +9156,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9193,10 +9177,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -9207,10 +9191,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9218,7 +9202,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>93</v>
@@ -9233,24 +9217,24 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="S56" t="s" s="2">
         <v>82</v>
@@ -9292,7 +9276,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9313,10 +9297,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9327,10 +9311,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9338,7 +9322,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>93</v>
@@ -9353,24 +9337,24 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
-        <v>408</v>
+        <v>82</v>
       </c>
       <c r="S57" t="s" s="2">
         <v>82</v>
@@ -9412,7 +9396,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9433,10 +9417,10 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9447,10 +9431,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9473,17 +9457,19 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>107</v>
+        <v>355</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>358</v>
+      </c>
       <c r="O58" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9532,7 +9518,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9553,10 +9539,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9567,10 +9553,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9593,19 +9579,19 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>360</v>
+        <v>107</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9654,7 +9640,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9675,10 +9661,10 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9687,12 +9673,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9700,13 +9686,13 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>82</v>
@@ -9715,19 +9701,19 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>107</v>
+        <v>410</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>370</v>
+        <v>411</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>371</v>
+        <v>412</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>372</v>
+        <v>413</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>373</v>
+        <v>414</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9776,7 +9762,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>374</v>
+        <v>409</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9791,30 +9777,30 @@
         <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>82</v>
+        <v>415</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>375</v>
+        <v>416</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>376</v>
+        <v>417</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9822,13 +9808,13 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>82</v>
@@ -9837,20 +9823,18 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9898,13 +9882,13 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
@@ -9913,19 +9897,19 @@
         <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>420</v>
+        <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>421</v>
+        <v>382</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>82</v>
@@ -9933,21 +9917,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>82</v>
+        <v>426</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9959,18 +9943,20 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -10018,13 +10004,13 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
@@ -10033,44 +10019,44 @@
         <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>387</v>
+        <v>433</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>82</v>
@@ -10079,19 +10065,19 @@
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -10140,7 +10126,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10149,50 +10135,50 @@
         <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>105</v>
+        <v>444</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>442</v>
+        <v>82</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>82</v>
@@ -10201,20 +10187,18 @@
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>443</v>
+        <v>129</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>447</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
@@ -10262,7 +10246,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10271,25 +10255,25 @@
         <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>448</v>
+        <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>449</v>
+        <v>105</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>450</v>
+        <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>82</v>
@@ -10297,10 +10281,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10311,7 +10295,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -10323,18 +10307,18 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>129</v>
+        <v>457</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10382,13 +10366,13 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
@@ -10397,19 +10381,19 @@
         <v>105</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>82</v>
+        <v>461</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>82</v>
@@ -10417,10 +10401,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10431,10 +10415,10 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>82</v>
@@ -10443,17 +10427,19 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>467</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>468</v>
+      </c>
       <c r="O66" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10490,59 +10476,59 @@
         <v>82</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="AC66" s="2"/>
       <c r="AD66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>82</v>
+        <v>471</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>82</v>
+        <v>472</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>466</v>
+        <v>82</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>82</v>
+        <v>473</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>469</v>
+        <v>82</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>82</v>
+        <v>476</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="C67" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>478</v>
+      </c>
       <c r="D67" t="s" s="2">
         <v>82</v>
       </c>
@@ -10563,19 +10549,19 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10612,17 +10598,19 @@
         <v>82</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="AC67" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>476</v>
+        <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10631,7 +10619,7 @@
         <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>105</v>
@@ -10640,31 +10628,29 @@
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="AN67" t="s" s="2">
+      <c r="B68" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="AO67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="C68" t="s" s="2">
-        <v>483</v>
-      </c>
+      <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10676,29 +10662,25 @@
         <v>93</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>471</v>
+        <v>107</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>472</v>
+        <v>108</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>474</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10746,7 +10728,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>470</v>
+        <v>110</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10755,47 +10737,47 @@
         <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>477</v>
+        <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>478</v>
+        <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>479</v>
+        <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>480</v>
+        <v>111</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>481</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -10807,15 +10789,17 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10852,31 +10836,31 @@
         <v>82</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10897,46 +10881,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>114</v>
+        <v>485</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>115</v>
+        <v>486</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>116</v>
+        <v>487</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O70" s="2"/>
+        <v>488</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10972,31 +10958,31 @@
         <v>82</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>121</v>
+        <v>490</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -11005,10 +10991,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>82</v>
+        <v>491</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>111</v>
+        <v>492</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -11017,12 +11003,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11030,39 +11016,39 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I71" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>490</v>
+        <v>173</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>493</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q71" s="2"/>
+      <c r="Q71" t="s" s="2">
+        <v>498</v>
+      </c>
       <c r="R71" t="s" s="2">
         <v>82</v>
       </c>
@@ -11082,13 +11068,13 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>82</v>
+        <v>499</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>82</v>
+        <v>500</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -11106,7 +11092,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11127,10 +11113,10 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11139,12 +11125,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11152,39 +11138,37 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J72" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q72" t="s" s="2">
-        <v>503</v>
-      </c>
+      <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
         <v>82</v>
       </c>
@@ -11204,13 +11188,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>504</v>
+        <v>82</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>505</v>
+        <v>82</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -11228,7 +11212,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11249,10 +11233,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11263,10 +11247,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11289,24 +11273,24 @@
         <v>94</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" t="s" s="2">
-        <v>82</v>
+        <v>517</v>
       </c>
       <c r="S73" t="s" s="2">
         <v>82</v>
@@ -11348,7 +11332,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11357,7 +11341,7 @@
         <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>82</v>
+        <v>519</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>105</v>
@@ -11369,10 +11353,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11383,10 +11367,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11409,24 +11393,26 @@
         <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>523</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>524</v>
+      </c>
       <c r="O74" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="S74" t="s" s="2">
         <v>82</v>
@@ -11468,7 +11454,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11477,7 +11463,7 @@
         <v>93</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>524</v>
+        <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>105</v>
@@ -11489,10 +11475,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11503,10 +11489,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11514,7 +11500,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>93</v>
@@ -11526,29 +11512,29 @@
         <v>82</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>173</v>
+        <v>289</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>531</v>
+        <v>82</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>82</v>
@@ -11566,13 +11552,13 @@
         <v>82</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>82</v>
+        <v>534</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>82</v>
+        <v>535</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
@@ -11590,7 +11576,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11599,7 +11585,7 @@
         <v>93</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>82</v>
+        <v>536</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>105</v>
@@ -11611,10 +11597,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>515</v>
+        <v>196</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11623,26 +11609,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>82</v>
+        <v>539</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>82</v>
@@ -11651,19 +11637,19 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11691,10 +11677,10 @@
         <v>155</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
@@ -11712,16 +11698,16 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>541</v>
+        <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>105</v>
@@ -11730,31 +11716,31 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>82</v>
+        <v>546</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>196</v>
+        <v>547</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>82</v>
+        <v>549</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>544</v>
+        <v>82</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11773,19 +11759,19 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>294</v>
+        <v>551</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11810,31 +11796,31 @@
         <v>82</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>549</v>
+        <v>82</v>
       </c>
       <c r="Z77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11852,27 +11838,27 @@
         <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>551</v>
+        <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>554</v>
+        <v>82</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11883,7 +11869,7 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>82</v>
@@ -11895,20 +11881,18 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>556</v>
+        <v>289</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>560</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11932,13 +11916,11 @@
         <v>82</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>82</v>
+        <v>562</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11956,13 +11938,13 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>82</v>
@@ -11974,27 +11956,27 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>82</v>
+        <v>563</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>82</v>
+        <v>566</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12008,7 +11990,7 @@
         <v>93</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>82</v>
@@ -12017,18 +11999,20 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="O79" s="2"/>
+        <v>570</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>571</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
       </c>
@@ -12052,29 +12036,29 @@
         <v>82</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF79" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12092,27 +12076,27 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>568</v>
+        <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>571</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12126,7 +12110,7 @@
         <v>93</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>82</v>
@@ -12135,20 +12119,16 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>294</v>
+        <v>107</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>573</v>
+        <v>108</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>576</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>82</v>
       </c>
@@ -12172,11 +12152,13 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="Y80" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z80" t="s" s="2">
-        <v>577</v>
+        <v>82</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -12194,7 +12176,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>572</v>
+        <v>110</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12206,7 +12188,7 @@
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -12215,10 +12197,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>578</v>
+        <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>579</v>
+        <v>111</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12229,21 +12211,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -12255,15 +12237,17 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12300,31 +12284,31 @@
         <v>82</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -12347,14 +12331,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12370,21 +12354,23 @@
         <v>82</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>115</v>
+        <v>307</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>116</v>
+        <v>308</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12420,19 +12406,19 @@
         <v>82</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>121</v>
+        <v>311</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12444,7 +12430,7 @@
         <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
@@ -12453,10 +12439,10 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>111</v>
+        <v>313</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12467,10 +12453,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12481,7 +12467,7 @@
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
@@ -12490,23 +12476,19 @@
         <v>82</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>312</v>
+        <v>108</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12554,19 +12536,19 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>316</v>
+        <v>110</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
@@ -12575,10 +12557,10 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>317</v>
+        <v>82</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>318</v>
+        <v>111</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12589,21 +12571,21 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
@@ -12615,15 +12597,17 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12660,31 +12644,31 @@
         <v>82</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12707,21 +12691,21 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>82</v>
@@ -12730,21 +12714,23 @@
         <v>82</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>115</v>
+        <v>320</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>116</v>
+        <v>321</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12780,31 +12766,31 @@
         <v>82</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>121</v>
+        <v>325</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
@@ -12813,10 +12799,10 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>82</v>
+        <v>326</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>111</v>
+        <v>327</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12827,10 +12813,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12838,7 +12824,7 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>93</v>
@@ -12853,20 +12839,18 @@
         <v>94</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12914,7 +12898,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12935,10 +12919,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12949,10 +12933,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12960,7 +12944,7 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>93</v>
@@ -12975,18 +12959,18 @@
         <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="O87" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -13034,7 +13018,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13055,10 +13039,10 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -13069,10 +13053,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13080,7 +13064,7 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>93</v>
@@ -13095,17 +13079,17 @@
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -13154,7 +13138,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13175,10 +13159,10 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13189,10 +13173,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13215,17 +13199,19 @@
         <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>107</v>
+        <v>355</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>358</v>
+      </c>
       <c r="O89" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -13274,7 +13260,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13295,10 +13281,10 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13309,10 +13295,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13335,19 +13321,19 @@
         <v>94</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>360</v>
+        <v>107</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -13396,7 +13382,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13417,10 +13403,10 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13431,10 +13417,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13454,23 +13440,21 @@
         <v>82</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>107</v>
+        <v>587</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>370</v>
+        <v>588</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>371</v>
+        <v>589</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>373</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13518,7 +13502,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>374</v>
+        <v>586</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13536,27 +13520,27 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>82</v>
+        <v>591</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>375</v>
+        <v>592</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>376</v>
+        <v>593</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>82</v>
+        <v>594</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13570,7 +13554,7 @@
         <v>93</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>82</v>
@@ -13579,16 +13563,16 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13638,7 +13622,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13656,27 +13640,27 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13687,10 +13671,10 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>82</v>
@@ -13699,18 +13683,20 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="O93" s="2"/>
+        <v>608</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>609</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
       </c>
@@ -13758,45 +13744,45 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>105</v>
+        <v>610</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>605</v>
+        <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>608</v>
+        <v>82</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13807,7 +13793,7 @@
         <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>82</v>
@@ -13819,20 +13805,16 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>610</v>
+        <v>107</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>611</v>
+        <v>108</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>614</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>82</v>
       </c>
@@ -13880,19 +13862,19 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>609</v>
+        <v>110</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>615</v>
+        <v>82</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>82</v>
@@ -13901,10 +13883,10 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>616</v>
+        <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>617</v>
+        <v>111</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13915,21 +13897,21 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>82</v>
@@ -13941,15 +13923,17 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13998,19 +13982,19 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>82</v>
@@ -14033,14 +14017,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>113</v>
+        <v>616</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -14053,24 +14037,26 @@
         <v>82</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K96" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>115</v>
+        <v>617</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>116</v>
+        <v>618</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O96" s="2"/>
+      <c r="O96" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
       </c>
@@ -14118,7 +14104,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>121</v>
+        <v>619</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14142,7 +14128,7 @@
         <v>82</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>111</v>
+        <v>196</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -14160,26 +14146,26 @@
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>621</v>
+        <v>82</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>114</v>
+        <v>621</v>
       </c>
       <c r="L97" t="s" s="2">
         <v>622</v>
@@ -14187,12 +14173,8 @@
       <c r="M97" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="N97" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>226</v>
-      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -14240,19 +14222,19 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI97" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="AG97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AJ97" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>82</v>
@@ -14261,10 +14243,10 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>82</v>
+        <v>625</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>196</v>
+        <v>626</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14275,10 +14257,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14301,13 +14283,13 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14358,7 +14340,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14367,7 +14349,7 @@
         <v>93</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>105</v>
@@ -14379,10 +14361,10 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AN98" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14393,10 +14375,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14419,16 +14401,20 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>626</v>
+        <v>289</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
+      <c r="O99" t="s" s="2">
+        <v>635</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
@@ -14452,13 +14438,13 @@
         <v>82</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>82</v>
+        <v>636</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>82</v>
+        <v>637</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
@@ -14476,7 +14462,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14485,7 +14471,7 @@
         <v>93</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>629</v>
+        <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>105</v>
@@ -14494,13 +14480,13 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>82</v>
+        <v>638</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>635</v>
+        <v>548</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14511,10 +14497,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14525,7 +14511,7 @@
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>82</v>
@@ -14537,19 +14523,19 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14574,13 +14560,13 @@
         <v>82</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>82</v>
@@ -14598,13 +14584,13 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>82</v>
@@ -14616,13 +14602,13 @@
         <v>82</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14633,10 +14619,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14647,7 +14633,7 @@
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>82</v>
@@ -14659,19 +14645,17 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>294</v>
+        <v>648</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>648</v>
-      </c>
+        <v>650</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14696,13 +14680,13 @@
         <v>82</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>650</v>
+        <v>82</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>651</v>
+        <v>82</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>82</v>
@@ -14720,13 +14704,13 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>82</v>
@@ -14738,13 +14722,13 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>643</v>
+        <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>644</v>
+        <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>553</v>
+        <v>652</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14755,10 +14739,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14781,7 +14765,7 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>653</v>
+        <v>107</v>
       </c>
       <c r="L102" t="s" s="2">
         <v>654</v>
@@ -14790,9 +14774,7 @@
         <v>655</v>
       </c>
       <c r="N102" s="2"/>
-      <c r="O102" t="s" s="2">
-        <v>656</v>
-      </c>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>82</v>
       </c>
@@ -14840,7 +14822,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14861,10 +14843,10 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>82</v>
+        <v>625</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14875,10 +14857,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14889,7 +14871,7 @@
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>82</v>
@@ -14898,10 +14880,10 @@
         <v>82</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>107</v>
+        <v>658</v>
       </c>
       <c r="L103" t="s" s="2">
         <v>659</v>
@@ -14909,7 +14891,9 @@
       <c r="M103" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="N103" s="2"/>
+      <c r="N103" t="s" s="2">
+        <v>661</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14958,13 +14942,13 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>82</v>
@@ -14979,10 +14963,10 @@
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>630</v>
+        <v>662</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14993,10 +14977,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15019,16 +15003,16 @@
         <v>94</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15078,7 +15062,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15099,10 +15083,10 @@
         <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -15111,12 +15095,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="105" hidden="true">
+    <row r="105">
       <c r="A105" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15130,7 +15114,7 @@
         <v>81</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>82</v>
@@ -15139,18 +15123,20 @@
         <v>94</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>670</v>
+        <v>605</v>
       </c>
       <c r="L105" t="s" s="2">
         <v>671</v>
       </c>
       <c r="M105" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="N105" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="N105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>673</v>
       </c>
-      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>82</v>
       </c>
@@ -15198,7 +15184,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15210,7 +15196,7 @@
         <v>82</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>105</v>
+        <v>674</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>82</v>
@@ -15219,10 +15205,10 @@
         <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -15231,12 +15217,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15247,32 +15233,28 @@
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>610</v>
+        <v>107</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>676</v>
+        <v>108</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>678</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>82</v>
       </c>
@@ -15320,19 +15302,19 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>675</v>
+        <v>110</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>679</v>
+        <v>82</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>82</v>
@@ -15341,10 +15323,10 @@
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>680</v>
+        <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>681</v>
+        <v>111</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15355,21 +15337,21 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>82</v>
@@ -15381,15 +15363,17 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N107" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -15438,19 +15422,19 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>82</v>
@@ -15473,14 +15457,14 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>113</v>
+        <v>616</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -15493,24 +15477,26 @@
         <v>82</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K108" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>115</v>
+        <v>617</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>116</v>
+        <v>618</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O108" s="2"/>
+      <c r="O108" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
       </c>
@@ -15558,7 +15544,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>121</v>
+        <v>619</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15582,7 +15568,7 @@
         <v>82</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>111</v>
+        <v>196</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15591,47 +15577,47 @@
         <v>82</v>
       </c>
     </row>
-    <row r="109" hidden="true">
+    <row r="109">
       <c r="A109" t="s" s="2">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>621</v>
+        <v>82</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J109" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>114</v>
+        <v>289</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>622</v>
+        <v>681</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>623</v>
+        <v>682</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>117</v>
+        <v>683</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>226</v>
+        <v>684</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15656,13 +15642,13 @@
         <v>82</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
@@ -15680,34 +15666,34 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>624</v>
+        <v>680</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>82</v>
+        <v>685</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>196</v>
+        <v>383</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>82</v>
+        <v>384</v>
       </c>
       <c r="AP109" t="s" s="2">
         <v>82</v>
@@ -15715,10 +15701,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15726,7 +15712,7 @@
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
         <v>93</v>
@@ -15741,19 +15727,19 @@
         <v>94</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>294</v>
+        <v>687</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>689</v>
+        <v>469</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15781,10 +15767,10 @@
         <v>155</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>383</v>
+        <v>691</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>384</v>
+        <v>692</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
@@ -15802,16 +15788,16 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>82</v>
+        <v>693</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>105</v>
@@ -15820,27 +15806,27 @@
         <v>82</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>387</v>
+        <v>474</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>388</v>
+        <v>475</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>389</v>
+        <v>82</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>82</v>
+        <v>476</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15860,22 +15846,22 @@
         <v>82</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>692</v>
+        <v>289</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>474</v>
+        <v>533</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15903,10 +15889,10 @@
         <v>155</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>696</v>
+        <v>534</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>697</v>
+        <v>535</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>82</v>
@@ -15924,7 +15910,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15933,7 +15919,7 @@
         <v>93</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>105</v>
@@ -15942,22 +15928,22 @@
         <v>82</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>699</v>
+        <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>479</v>
+        <v>196</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>480</v>
+        <v>537</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>481</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
         <v>700</v>
       </c>
@@ -15966,17 +15952,17 @@
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>82</v>
+        <v>539</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>82</v>
@@ -15985,19 +15971,19 @@
         <v>82</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>701</v>
+        <v>540</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>702</v>
+        <v>541</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>703</v>
+        <v>542</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -16025,10 +16011,10 @@
         <v>155</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>82</v>
@@ -16052,10 +16038,10 @@
         <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>704</v>
+        <v>82</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>105</v>
@@ -16064,31 +16050,31 @@
         <v>82</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>82</v>
+        <v>546</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>196</v>
+        <v>547</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>82</v>
+        <v>549</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>544</v>
+        <v>82</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -16107,19 +16093,19 @@
         <v>82</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>545</v>
+        <v>702</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>546</v>
+        <v>703</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>547</v>
+        <v>608</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>548</v>
+        <v>609</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -16144,13 +16130,13 @@
         <v>82</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>549</v>
+        <v>82</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>550</v>
+        <v>82</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>82</v>
@@ -16168,7 +16154,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16186,145 +16172,23 @@
         <v>82</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>551</v>
+        <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>552</v>
+        <v>611</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>553</v>
+        <v>612</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="114" hidden="true">
-      <c r="A114" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="C114" s="2"/>
-      <c r="D114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E114" s="2"/>
-      <c r="F114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="P114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q114" s="2"/>
-      <c r="R114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="AO114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP114" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP114">
+  <autoFilter ref="A1:AP113">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16334,7 +16198,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI113">
+  <conditionalFormatting sqref="A2:AI112">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
